--- a/exports/trend_1d/HEROMOTOCO_full_report.xlsx
+++ b/exports/trend_1d/HEROMOTOCO_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q82"/>
+  <dimension ref="A1:U82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>6.11</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42040</v>
+        <v>42041</v>
       </c>
       <c r="H2" t="n">
-        <v>2680.05</v>
+        <v>2610.8</v>
       </c>
       <c r="I2" t="n">
         <v>2611.026</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.62</v>
+        <v>-6.11</v>
       </c>
       <c r="L2" t="n">
         <v>7.04</v>
@@ -555,7 +578,7 @@
         <v>1.56</v>
       </c>
       <c r="N2" t="n">
-        <v>2.02</v>
+        <v>2.58</v>
       </c>
       <c r="O2" t="n">
         <v>1.7</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>9.050000000000001</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42136</v>
+        <v>42137</v>
       </c>
       <c r="H3" t="n">
-        <v>2308.5</v>
+        <v>2344.9</v>
       </c>
       <c r="I3" t="n">
         <v>2322.243001962786</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K3" t="n">
-        <v>11.58</v>
+        <v>10.18</v>
       </c>
       <c r="L3" t="n">
         <v>3.43</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42061</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>4</v>
+      </c>
+      <c r="U3" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.039999999999999</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42212</v>
+        <v>42213</v>
       </c>
       <c r="H4" t="n">
-        <v>2443.75</v>
+        <v>2372</v>
       </c>
       <c r="I4" t="n">
         <v>2416.920093236247</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K4" t="n">
-        <v>4.22</v>
+        <v>1.16</v>
       </c>
       <c r="L4" t="n">
         <v>0.97</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42278</v>
+        <v>42282</v>
       </c>
       <c r="H5" t="n">
-        <v>2255.45</v>
+        <v>2343.2</v>
       </c>
       <c r="I5" t="n">
         <v>2334.932609319085</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K5" t="n">
-        <v>4.91</v>
+        <v>1.21</v>
       </c>
       <c r="L5" t="n">
         <v>10.79</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42374</v>
+        <v>42375</v>
       </c>
       <c r="H6" t="n">
-        <v>2455.25</v>
+        <v>2417.55</v>
       </c>
       <c r="I6" t="n">
         <v>2427.127199441146</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K6" t="n">
-        <v>4.78</v>
+        <v>3.17</v>
       </c>
       <c r="L6" t="n">
         <v>2.79</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42306</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>4</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>6.19</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42390</v>
+        <v>42391</v>
       </c>
       <c r="H7" t="n">
-        <v>2311.9</v>
+        <v>2430.5</v>
       </c>
       <c r="I7" t="n">
         <v>2415.286003540165</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K7" t="n">
-        <v>4.37</v>
+        <v>-0.54</v>
       </c>
       <c r="L7" t="n">
         <v>1.81</v>
       </c>
       <c r="M7" t="n">
-        <v>0.83</v>
+        <v>1.02</v>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>5.13</v>
       </c>
       <c r="O7" t="n">
         <v>-1.54</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>9.960000000000001</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42492</v>
+        <v>42493</v>
       </c>
       <c r="H8" t="n">
-        <v>2735.7</v>
+        <v>2717.25</v>
       </c>
       <c r="I8" t="n">
         <v>2720.762284001923</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K8" t="n">
-        <v>12.56</v>
+        <v>11.8</v>
       </c>
       <c r="L8" t="n">
         <v>6.44</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>5</v>
+      </c>
+      <c r="U8" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>8.4</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42517</v>
+        <v>42520</v>
       </c>
       <c r="H9" t="n">
-        <v>2831.45</v>
+        <v>2924.15</v>
       </c>
       <c r="I9" t="n">
         <v>2876.678800963201</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K9" t="n">
-        <v>-4.2</v>
+        <v>-7.61</v>
       </c>
       <c r="L9" t="n">
-        <v>4.47</v>
+        <v>7.97</v>
       </c>
       <c r="M9" t="n">
         <v>1.98</v>
       </c>
       <c r="N9" t="n">
-        <v>1.91</v>
+        <v>3.27</v>
       </c>
       <c r="O9" t="n">
         <v>-0.67</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42516</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>7.22</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42641</v>
+        <v>42642</v>
       </c>
       <c r="H10" t="n">
-        <v>3269.45</v>
+        <v>3246.8</v>
       </c>
       <c r="I10" t="n">
         <v>3251.238774192209</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K10" t="n">
-        <v>11.81</v>
+        <v>11.03</v>
       </c>
       <c r="L10" t="n">
         <v>4.77</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42551</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.18</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42711</v>
+        <v>42712</v>
       </c>
       <c r="H11" t="n">
-        <v>3051.65</v>
+        <v>3137.55</v>
       </c>
       <c r="I11" t="n">
         <v>3055.446009486577</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K11" t="n">
-        <v>6.01</v>
+        <v>3.36</v>
       </c>
       <c r="L11" t="n">
         <v>4.98</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>8.66</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42724</v>
+        <v>42725</v>
       </c>
       <c r="H12" t="n">
-        <v>2886.5</v>
+        <v>2850.25</v>
       </c>
       <c r="I12" t="n">
         <v>2882.970878903037</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K12" t="n">
-        <v>-8</v>
+        <v>-9.16</v>
       </c>
       <c r="L12" t="n">
-        <v>8.43</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="M12" t="n">
         <v>0.73</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>9.220000000000001</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42759</v>
+        <v>42760</v>
       </c>
       <c r="H13" t="n">
-        <v>2960.05</v>
+        <v>3070.4</v>
       </c>
       <c r="I13" t="n">
         <v>3022.976335348912</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.85</v>
+        <v>-7.72</v>
       </c>
       <c r="L13" t="n">
-        <v>4.68</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M13" t="n">
         <v>1.03</v>
       </c>
       <c r="N13" t="n">
-        <v>2.3</v>
+        <v>3.73</v>
       </c>
       <c r="O13" t="n">
         <v>-1.26</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42999</v>
+        <v>43000</v>
       </c>
       <c r="H14" t="n">
-        <v>3703.5</v>
+        <v>3600.8</v>
       </c>
       <c r="I14" t="n">
         <v>3602.588716456268</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K14" t="n">
-        <v>20.62</v>
+        <v>17.27</v>
       </c>
       <c r="L14" t="n">
         <v>6.3</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>163</v>
+        <v>164</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42789</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>8</v>
+      </c>
+      <c r="U14" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>7.32</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>43087</v>
+        <v>43088</v>
       </c>
       <c r="H15" t="n">
-        <v>3351.25</v>
+        <v>3512.85</v>
       </c>
       <c r="I15" t="n">
         <v>3449.949493573215</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K15" t="n">
-        <v>6.93</v>
+        <v>2.44</v>
       </c>
       <c r="L15" t="n">
         <v>2.49</v>
@@ -1296,7 +1475,7 @@
         <v>1.78</v>
       </c>
       <c r="N15" t="n">
-        <v>2.17</v>
+        <v>4.82</v>
       </c>
       <c r="O15" t="n">
         <v>-2.77</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>43006</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>8.73</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>43116</v>
+        <v>43117</v>
       </c>
       <c r="H16" t="n">
-        <v>3400.75</v>
+        <v>3382</v>
       </c>
       <c r="I16" t="n">
         <v>3393.674095268669</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.19</v>
+        <v>-3.72</v>
       </c>
       <c r="L16" t="n">
-        <v>4.47</v>
+        <v>4.85</v>
       </c>
       <c r="M16" t="n">
         <v>0.67</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>43097</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.43</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>43168</v>
+        <v>43171</v>
       </c>
       <c r="H17" t="n">
-        <v>3401</v>
+        <v>3506.5</v>
       </c>
       <c r="I17" t="n">
         <v>3500.679022546316</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-3.68</v>
       </c>
       <c r="L17" t="n">
         <v>5.35</v>
@@ -1410,7 +1613,7 @@
         <v>2.24</v>
       </c>
       <c r="N17" t="n">
-        <v>2.03</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
         <v>-0.55</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>43125</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>6.74</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>43179</v>
+        <v>43180</v>
       </c>
       <c r="H18" t="n">
-        <v>3330.25</v>
+        <v>3281.25</v>
       </c>
       <c r="I18" t="n">
         <v>3314.361316420078</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K18" t="n">
-        <v>-5.03</v>
+        <v>-6.42</v>
       </c>
       <c r="L18" t="n">
-        <v>5.67</v>
+        <v>6.65</v>
       </c>
       <c r="M18" t="n">
         <v>0.59</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>7.11</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43187</v>
+        <v>43192</v>
       </c>
       <c r="H19" t="n">
-        <v>3358.55</v>
+        <v>3459.2</v>
       </c>
       <c r="I19" t="n">
         <v>3421.685548623472</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.36</v>
+        <v>-5.42</v>
       </c>
       <c r="L19" t="n">
-        <v>3.43</v>
+        <v>5.68</v>
       </c>
       <c r="M19" t="n">
         <v>0.47</v>
       </c>
       <c r="N19" t="n">
-        <v>2.32</v>
+        <v>3</v>
       </c>
       <c r="O19" t="n">
         <v>-1.47</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>43187</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.19</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43236</v>
+        <v>43237</v>
       </c>
       <c r="H20" t="n">
-        <v>3390.45</v>
+        <v>3370</v>
       </c>
       <c r="I20" t="n">
         <v>3377.92906414624</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.99</v>
+        <v>-2.58</v>
       </c>
       <c r="L20" t="n">
         <v>4.07</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43216</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>6.03</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43262</v>
+        <v>43263</v>
       </c>
       <c r="H21" t="n">
-        <v>3426.35</v>
+        <v>3500.05</v>
       </c>
       <c r="I21" t="n">
         <v>3482.17822797775</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.67</v>
+        <v>-3.86</v>
       </c>
       <c r="L21" t="n">
-        <v>3.34</v>
+        <v>4.56</v>
       </c>
       <c r="M21" t="n">
         <v>1.23</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43251</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>6.56</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43279</v>
+        <v>43280</v>
       </c>
       <c r="H22" t="n">
-        <v>3332.45</v>
+        <v>3290.95</v>
       </c>
       <c r="I22" t="n">
         <v>3318.250669383988</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K22" t="n">
-        <v>-4.79</v>
+        <v>-5.97</v>
       </c>
       <c r="L22" t="n">
-        <v>5.91</v>
+        <v>6.45</v>
       </c>
       <c r="M22" t="n">
         <v>0.48</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.04</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43420</v>
+        <v>43423</v>
       </c>
       <c r="H23" t="n">
-        <v>2791.85</v>
+        <v>2810.15</v>
       </c>
       <c r="I23" t="n">
         <v>2799.458503140016</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="K23" t="n">
-        <v>15.17</v>
+        <v>14.61</v>
       </c>
       <c r="L23" t="n">
         <v>5.82</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43307</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>5</v>
+      </c>
+      <c r="U23" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>9.4</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43466</v>
+        <v>43467</v>
       </c>
       <c r="H24" t="n">
-        <v>2953.5</v>
+        <v>2874.45</v>
       </c>
       <c r="I24" t="n">
         <v>2915.200547865493</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K24" t="n">
-        <v>5.1</v>
+        <v>2.29</v>
       </c>
       <c r="L24" t="n">
         <v>3.77</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43433</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>9.52</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43500</v>
+        <v>43501</v>
       </c>
       <c r="H25" t="n">
-        <v>2614.55</v>
+        <v>2687.15</v>
       </c>
       <c r="I25" t="n">
         <v>2665.220771294557</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K25" t="n">
-        <v>9.039999999999999</v>
+        <v>6.52</v>
       </c>
       <c r="L25" t="n">
         <v>2.4</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>11.1</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43514</v>
+        <v>43515</v>
       </c>
       <c r="H26" t="n">
-        <v>2520.3</v>
+        <v>2474.75</v>
       </c>
       <c r="I26" t="n">
         <v>2520.273357982449</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K26" t="n">
-        <v>-6.21</v>
+        <v>-7.9</v>
       </c>
       <c r="L26" t="n">
-        <v>7.05</v>
+        <v>8.19</v>
       </c>
       <c r="M26" t="n">
         <v>0.85</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>12.26</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43570</v>
+        <v>43571</v>
       </c>
       <c r="H27" t="n">
-        <v>2537.05</v>
+        <v>2575.05</v>
       </c>
       <c r="I27" t="n">
         <v>2569.738428003347</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K27" t="n">
-        <v>-2.52</v>
+        <v>-4.05</v>
       </c>
       <c r="L27" t="n">
         <v>8.380000000000001</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,28 +2351,28 @@
         <v>6.55</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43581</v>
+        <v>43585</v>
       </c>
       <c r="H28" t="n">
-        <v>2442.7</v>
+        <v>2352.8</v>
       </c>
       <c r="I28" t="n">
         <v>2428.039624375783</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K28" t="n">
-        <v>-5.14</v>
+        <v>-8.630000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>6.29</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>0.09</v>
+        <v>1.24</v>
       </c>
       <c r="N28" t="n">
-        <v>1.99</v>
+        <v>3.68</v>
       </c>
       <c r="O28" t="n">
         <v>1.5</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43580</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2073,25 +2420,25 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43602</v>
+        <v>43605</v>
       </c>
       <c r="H29" t="n">
-        <v>2460.8</v>
+        <v>2549.5</v>
       </c>
       <c r="I29" t="n">
         <v>2517.029044105303</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K29" t="n">
-        <v>-4.59</v>
+        <v>-8.359999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>5.19</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>1.51</v>
+        <v>2.67</v>
       </c>
       <c r="N29" t="n">
         <v>4.22</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>9.1</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>43637</v>
+        <v>43640</v>
       </c>
       <c r="H30" t="n">
-        <v>2444.65</v>
+        <v>2425.4</v>
       </c>
       <c r="I30" t="n">
         <v>2439.598583779996</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K30" t="n">
-        <v>-4.11</v>
+        <v>-4.87</v>
       </c>
       <c r="L30" t="n">
-        <v>5.39</v>
+        <v>6.61</v>
       </c>
       <c r="M30" t="n">
         <v>0.34</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43615</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>8.69</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>43685</v>
+        <v>43686</v>
       </c>
       <c r="H31" t="n">
-        <v>2427</v>
+        <v>2460.5</v>
       </c>
       <c r="I31" t="n">
         <v>2452.056820415663</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-1.45</v>
       </c>
       <c r="L31" t="n">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="M31" t="n">
         <v>1.22</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>43643</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>11.79</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>43726</v>
+        <v>43727</v>
       </c>
       <c r="H32" t="n">
-        <v>2415.5</v>
+        <v>2372.7</v>
       </c>
       <c r="I32" t="n">
         <v>2379.227243334308</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.83</v>
+        <v>-3.57</v>
       </c>
       <c r="L32" t="n">
-        <v>4.17</v>
+        <v>4.31</v>
       </c>
       <c r="M32" t="n">
         <v>2.86</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>43706</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>11.66</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>43727</v>
+        <v>43728</v>
       </c>
       <c r="H33" t="n">
-        <v>2372.7</v>
+        <v>2695.25</v>
       </c>
       <c r="I33" t="n">
         <v>2649.38381460929</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>-13.59</v>
       </c>
       <c r="L33" t="n">
-        <v>2.58</v>
+        <v>19.91</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>13.59</v>
       </c>
       <c r="O33" t="n">
         <v>-1.77</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>16.97</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>43787</v>
+        <v>43788</v>
       </c>
       <c r="H34" t="n">
-        <v>2344.1</v>
+        <v>2310.95</v>
       </c>
       <c r="I34" t="n">
         <v>2336.348855248529</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K34" t="n">
-        <v>-13.03</v>
+        <v>-14.26</v>
       </c>
       <c r="L34" t="n">
-        <v>13.25</v>
+        <v>14.47</v>
       </c>
       <c r="M34" t="n">
         <v>0.75</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>8.75</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>43826</v>
+        <v>43829</v>
       </c>
       <c r="H35" t="n">
-        <v>2285.1</v>
+        <v>2320.8</v>
       </c>
       <c r="I35" t="n">
         <v>2300.073096319366</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K35" t="n">
-        <v>1.12</v>
+        <v>-0.43</v>
       </c>
       <c r="L35" t="n">
         <v>2.75</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,25 +2903,25 @@
         <v>6.74</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>43837</v>
+        <v>43838</v>
       </c>
       <c r="H36" t="n">
-        <v>2193</v>
+        <v>2163.25</v>
       </c>
       <c r="I36" t="n">
         <v>2164.483941432045</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K36" t="n">
-        <v>-5.51</v>
+        <v>-6.79</v>
       </c>
       <c r="L36" t="n">
-        <v>5.97</v>
+        <v>7.08</v>
       </c>
       <c r="M36" t="n">
-        <v>0.53</v>
+        <v>1.16</v>
       </c>
       <c r="N36" t="n">
         <v>2.75</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S36" t="b">
+        <v>0</v>
+      </c>
+      <c r="T36" t="n">
+        <v>1</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>6.89</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>43844</v>
+        <v>43845</v>
       </c>
       <c r="H37" t="n">
-        <v>2254.8</v>
+        <v>2318.15</v>
       </c>
       <c r="I37" t="n">
         <v>2312.340855583271</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.23</v>
+        <v>-7.16</v>
       </c>
       <c r="L37" t="n">
-        <v>4.57</v>
+        <v>7.35</v>
       </c>
       <c r="M37" t="n">
         <v>1.06</v>
       </c>
       <c r="N37" t="n">
-        <v>1.97</v>
+        <v>2.81</v>
       </c>
       <c r="O37" t="n">
         <v>-1.36</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>7.34</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>43875</v>
+        <v>43878</v>
       </c>
       <c r="H38" t="n">
-        <v>2201.25</v>
+        <v>2129.9</v>
       </c>
       <c r="I38" t="n">
         <v>2200.776218606783</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.04</v>
+        <v>-8.119999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>5.5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="M38" t="n">
         <v>2.38</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.7</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>43950</v>
+        <v>43951</v>
       </c>
       <c r="H39" t="n">
-        <v>1824.45</v>
+        <v>2016.1</v>
       </c>
       <c r="I39" t="n">
         <v>1876.251137514446</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K39" t="n">
-        <v>14.34</v>
+        <v>5.34</v>
       </c>
       <c r="L39" t="n">
         <v>2.37</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>21.01</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44043</v>
+        <v>44046</v>
       </c>
       <c r="H40" t="n">
-        <v>2513.45</v>
+        <v>2469.35</v>
       </c>
       <c r="I40" t="n">
         <v>2469.656506181545</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K40" t="n">
-        <v>24.67</v>
+        <v>22.48</v>
       </c>
       <c r="L40" t="n">
         <v>11.29</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>43979</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>4</v>
+      </c>
+      <c r="U40" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>13.11</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44061</v>
+        <v>44062</v>
       </c>
       <c r="H41" t="n">
-        <v>2755</v>
+        <v>2763.7</v>
       </c>
       <c r="I41" t="n">
         <v>2760.581438183237</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K41" t="n">
-        <v>-11.57</v>
+        <v>-11.92</v>
       </c>
       <c r="L41" t="n">
-        <v>13.14</v>
+        <v>14.52</v>
       </c>
       <c r="M41" t="n">
         <v>1.28</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>7.65</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44078</v>
+        <v>44081</v>
       </c>
       <c r="H42" t="n">
-        <v>2746.3</v>
+        <v>2692.6</v>
       </c>
       <c r="I42" t="n">
         <v>2695.043725940004</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.63</v>
+        <v>-2.57</v>
       </c>
       <c r="L42" t="n">
-        <v>2.31</v>
+        <v>2.86</v>
       </c>
       <c r="M42" t="n">
         <v>0.79</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>12.06</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44102</v>
+        <v>44103</v>
       </c>
       <c r="H43" t="n">
-        <v>2915.75</v>
+        <v>2999.7</v>
       </c>
       <c r="I43" t="n">
         <v>2983.739087274967</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K43" t="n">
-        <v>-8.289999999999999</v>
+        <v>-11.41</v>
       </c>
       <c r="L43" t="n">
-        <v>9.57</v>
+        <v>13.11</v>
       </c>
       <c r="M43" t="n">
         <v>1.55</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>9.26</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44125</v>
+        <v>44126</v>
       </c>
       <c r="H44" t="n">
-        <v>3003</v>
+        <v>2908.5</v>
       </c>
       <c r="I44" t="n">
         <v>2926.069548562784</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K44" t="n">
-        <v>0.11</v>
+        <v>-3.04</v>
       </c>
       <c r="L44" t="n">
-        <v>2.63</v>
+        <v>3.66</v>
       </c>
       <c r="M44" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="N44" t="n">
-        <v>3.01</v>
+        <v>3.15</v>
       </c>
       <c r="O44" t="n">
         <v>2.88</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>10.7</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44168</v>
+        <v>44169</v>
       </c>
       <c r="H45" t="n">
-        <v>2965.45</v>
+        <v>3005.05</v>
       </c>
       <c r="I45" t="n">
         <v>2998.285121926972</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.96</v>
+        <v>-3.32</v>
       </c>
       <c r="L45" t="n">
-        <v>3.21</v>
+        <v>4.04</v>
       </c>
       <c r="M45" t="n">
         <v>3.27</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>3</v>
+      </c>
+      <c r="U45" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>7.97</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44252</v>
+        <v>44253</v>
       </c>
       <c r="H46" t="n">
-        <v>3252.8</v>
+        <v>3047.55</v>
       </c>
       <c r="I46" t="n">
         <v>3061.051927222361</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K46" t="n">
-        <v>8.24</v>
+        <v>1.41</v>
       </c>
       <c r="L46" t="n">
         <v>9.08</v>
@@ -3063,7 +3614,7 @@
         <v>1.03</v>
       </c>
       <c r="N46" t="n">
-        <v>4.65</v>
+        <v>6.31</v>
       </c>
       <c r="O46" t="n">
         <v>1.34</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>58</v>
+        <v>59</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>4</v>
+      </c>
+      <c r="U46" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>14.43</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44350</v>
+        <v>44351</v>
       </c>
       <c r="H47" t="n">
-        <v>2837.15</v>
+        <v>2876.25</v>
       </c>
       <c r="I47" t="n">
         <v>2847.373863930017</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K47" t="n">
-        <v>6.9</v>
+        <v>5.62</v>
       </c>
       <c r="L47" t="n">
         <v>9.18</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>4</v>
+      </c>
+      <c r="U47" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>7.31</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44396</v>
+        <v>44397</v>
       </c>
       <c r="H48" t="n">
-        <v>2718.9</v>
+        <v>2671.95</v>
       </c>
       <c r="I48" t="n">
         <v>2710.488496286597</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K48" t="n">
-        <v>-5.47</v>
+        <v>-7.1</v>
       </c>
       <c r="L48" t="n">
-        <v>6.66</v>
+        <v>7.48</v>
       </c>
       <c r="M48" t="n">
         <v>0.99</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>5.5</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>44442</v>
+        <v>44445</v>
       </c>
       <c r="H49" t="n">
-        <v>2633.4</v>
+        <v>2650.7</v>
       </c>
       <c r="I49" t="n">
         <v>2633.42821770052</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K49" t="n">
-        <v>1.44</v>
+        <v>0.8</v>
       </c>
       <c r="L49" t="n">
         <v>2.19</v>
       </c>
       <c r="M49" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N49" t="n">
         <v>2.63</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>5.29</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>44489</v>
+        <v>44490</v>
       </c>
       <c r="H50" t="n">
-        <v>2649.5</v>
+        <v>2591.85</v>
       </c>
       <c r="I50" t="n">
         <v>2618.154107619065</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.05</v>
+        <v>-2.22</v>
       </c>
       <c r="L50" t="n">
-        <v>2</v>
+        <v>3.39</v>
       </c>
       <c r="M50" t="n">
         <v>1.04</v>
       </c>
       <c r="N50" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="O50" t="n">
         <v>0.66</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>7.47</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>44568</v>
+        <v>44571</v>
       </c>
       <c r="H51" t="n">
-        <v>2340.4</v>
+        <v>2417.45</v>
       </c>
       <c r="I51" t="n">
         <v>2368.114468920428</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="K51" t="n">
-        <v>9.699999999999999</v>
+        <v>6.73</v>
       </c>
       <c r="L51" t="n">
         <v>2.94</v>
@@ -3348,7 +3959,7 @@
         <v>2.01</v>
       </c>
       <c r="N51" t="n">
-        <v>2.22</v>
+        <v>3.29</v>
       </c>
       <c r="O51" t="n">
         <v>-2.18</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>44497</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>4</v>
+      </c>
+      <c r="U51" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>7.49</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>44615</v>
+        <v>44616</v>
       </c>
       <c r="H52" t="n">
-        <v>2507.75</v>
+        <v>2331.9</v>
       </c>
       <c r="I52" t="n">
         <v>2409.903741465946</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="K52" t="n">
-        <v>3.74</v>
+        <v>-3.54</v>
       </c>
       <c r="L52" t="n">
-        <v>3.58</v>
+        <v>5.57</v>
       </c>
       <c r="M52" t="n">
         <v>2.43</v>
       </c>
       <c r="N52" t="n">
-        <v>2.81</v>
+        <v>7.01</v>
       </c>
       <c r="O52" t="n">
         <v>3.29</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>2</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>14.53</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>44677</v>
+        <v>44678</v>
       </c>
       <c r="H53" t="n">
-        <v>2250.8</v>
+        <v>2341.25</v>
       </c>
       <c r="I53" t="n">
         <v>2308.984629875559</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K53" t="n">
-        <v>3.48</v>
+        <v>-0.4</v>
       </c>
       <c r="L53" t="n">
         <v>5.61</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>11.8</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>44715</v>
+        <v>44718</v>
       </c>
       <c r="H54" t="n">
-        <v>2422.95</v>
+        <v>2381</v>
       </c>
       <c r="I54" t="n">
         <v>2391.62224604315</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K54" t="n">
-        <v>3.49</v>
+        <v>1.7</v>
       </c>
       <c r="L54" t="n">
         <v>5.42</v>
@@ -3528,7 +4175,19 @@
         <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>3</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,22 +4214,22 @@
         <v>10.84</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>44735</v>
+        <v>44736</v>
       </c>
       <c r="H55" t="n">
-        <v>2511.1</v>
+        <v>2594.85</v>
       </c>
       <c r="I55" t="n">
         <v>2529.916607881678</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K55" t="n">
-        <v>-5.46</v>
+        <v>-8.98</v>
       </c>
       <c r="L55" t="n">
-        <v>5.98</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="M55" t="n">
         <v>1.99</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>10.7</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>44819</v>
+        <v>44820</v>
       </c>
       <c r="H56" t="n">
-        <v>2624.45</v>
+        <v>2521.9</v>
       </c>
       <c r="I56" t="n">
         <v>2565.439807592685</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K56" t="n">
-        <v>1.14</v>
+        <v>-2.81</v>
       </c>
       <c r="L56" t="n">
-        <v>2.88</v>
+        <v>3.38</v>
       </c>
       <c r="M56" t="n">
         <v>1.44</v>
       </c>
       <c r="N56" t="n">
-        <v>2.53</v>
+        <v>3.91</v>
       </c>
       <c r="O56" t="n">
         <v>3.34</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>4</v>
+      </c>
+      <c r="U56" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>9.32</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>44879</v>
+        <v>44880</v>
       </c>
       <c r="H57" t="n">
-        <v>2525.05</v>
+        <v>2566.35</v>
       </c>
       <c r="I57" t="n">
         <v>2562.384545729391</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="K57" t="n">
-        <v>-0.12</v>
+        <v>-1.76</v>
       </c>
       <c r="L57" t="n">
         <v>5.34</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>3</v>
+      </c>
+      <c r="U57" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>6.75</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>44917</v>
+        <v>44918</v>
       </c>
       <c r="H58" t="n">
-        <v>2563.4</v>
+        <v>2474.75</v>
       </c>
       <c r="I58" t="n">
         <v>2530.357053914953</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.11</v>
+        <v>-3.57</v>
       </c>
       <c r="L58" t="n">
-        <v>3.23</v>
+        <v>3.88</v>
       </c>
       <c r="M58" t="n">
         <v>0.97</v>
       </c>
       <c r="N58" t="n">
-        <v>1.85</v>
+        <v>3.46</v>
       </c>
       <c r="O58" t="n">
         <v>1.64</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>8.69</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H59" t="n">
-        <v>2192.35</v>
+        <v>2274.05</v>
       </c>
       <c r="I59" t="n">
         <v>2253.447376361599</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="K59" t="n">
-        <v>11.41</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="L59" t="n">
         <v>7.33</v>
       </c>
       <c r="M59" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="N59" t="n">
-        <v>2.54</v>
+        <v>3.73</v>
       </c>
       <c r="O59" t="n">
         <v>-3.46</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>5</v>
+      </c>
+      <c r="U59" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>7.76</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45093</v>
+        <v>45096</v>
       </c>
       <c r="H60" t="n">
-        <v>2665.2</v>
+        <v>2616.95</v>
       </c>
       <c r="I60" t="n">
         <v>2643.604891973422</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K60" t="n">
-        <v>17.2</v>
+        <v>15.08</v>
       </c>
       <c r="L60" t="n">
         <v>2.53</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>8.24</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45110</v>
+        <v>45111</v>
       </c>
       <c r="H61" t="n">
-        <v>2730.25</v>
+        <v>2858.1</v>
       </c>
       <c r="I61" t="n">
         <v>2807.375061725349</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K61" t="n">
-        <v>-4.33</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>5.12</v>
+        <v>9.59</v>
       </c>
       <c r="M61" t="n">
-        <v>0.41</v>
+        <v>1.87</v>
       </c>
       <c r="N61" t="n">
-        <v>2.98</v>
+        <v>4.68</v>
       </c>
       <c r="O61" t="n">
         <v>-1.81</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,28 +4697,28 @@
         <v>9.109999999999999</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45139</v>
+        <v>45140</v>
       </c>
       <c r="H62" t="n">
-        <v>2928.6</v>
+        <v>2822.65</v>
       </c>
       <c r="I62" t="n">
         <v>2841.709816688952</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K62" t="n">
-        <v>2.47</v>
+        <v>-1.24</v>
       </c>
       <c r="L62" t="n">
         <v>3.89</v>
       </c>
       <c r="M62" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="N62" t="n">
-        <v>3.27</v>
+        <v>3.62</v>
       </c>
       <c r="O62" t="n">
         <v>4.68</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>9.6</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45184</v>
+        <v>45187</v>
       </c>
       <c r="H63" t="n">
-        <v>2892.3</v>
+        <v>2940.85</v>
       </c>
       <c r="I63" t="n">
         <v>2927.26109937905</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K63" t="n">
-        <v>-2.47</v>
+        <v>-4.19</v>
       </c>
       <c r="L63" t="n">
-        <v>3.79</v>
+        <v>4.65</v>
       </c>
       <c r="M63" t="n">
         <v>1.79</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.24</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="H64" t="n">
-        <v>4386.05</v>
+        <v>4321.6</v>
       </c>
       <c r="I64" t="n">
         <v>4325.807244605587</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="K64" t="n">
-        <v>49.14</v>
+        <v>46.95</v>
       </c>
       <c r="L64" t="n">
         <v>6.32</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>110</v>
+        <v>111</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>6</v>
+      </c>
+      <c r="U64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>9.029999999999999</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45419</v>
+        <v>45420</v>
       </c>
       <c r="H65" t="n">
-        <v>4367.15</v>
+        <v>4500.95</v>
       </c>
       <c r="I65" t="n">
         <v>4452.338344561232</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K65" t="n">
-        <v>-1.05</v>
+        <v>-4.15</v>
       </c>
       <c r="L65" t="n">
         <v>7.89</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>4</v>
+      </c>
+      <c r="U65" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>9.34</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45505</v>
+        <v>45506</v>
       </c>
       <c r="H66" t="n">
-        <v>5240.35</v>
+        <v>5145.1</v>
       </c>
       <c r="I66" t="n">
         <v>5196.834757325608</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K66" t="n">
-        <v>16.43</v>
+        <v>14.31</v>
       </c>
       <c r="L66" t="n">
         <v>4.32</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>4</v>
+      </c>
+      <c r="U66" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45534</v>
+        <v>45537</v>
       </c>
       <c r="H67" t="n">
-        <v>5321.85</v>
+        <v>5441.65</v>
       </c>
       <c r="I67" t="n">
         <v>5395.447417493673</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K67" t="n">
-        <v>-3.44</v>
+        <v>-5.76</v>
       </c>
       <c r="L67" t="n">
-        <v>4.62</v>
+        <v>6.73</v>
       </c>
       <c r="M67" t="n">
-        <v>1.09</v>
+        <v>1.46</v>
       </c>
       <c r="N67" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="O67" t="n">
         <v>-1.82</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>7.14</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45562</v>
+        <v>45565</v>
       </c>
       <c r="H68" t="n">
-        <v>5811.55</v>
+        <v>5572.6</v>
       </c>
       <c r="I68" t="n">
         <v>5613.712234192366</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K68" t="n">
-        <v>6.8</v>
+        <v>2.41</v>
       </c>
       <c r="L68" t="n">
         <v>1.1</v>
@@ -4317,7 +5132,7 @@
         <v>1.36</v>
       </c>
       <c r="N68" t="n">
-        <v>1.56</v>
+        <v>4.11</v>
       </c>
       <c r="O68" t="n">
         <v>2.25</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>9.630000000000001</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45687</v>
+        <v>45688</v>
       </c>
       <c r="H69" t="n">
-        <v>4075.55</v>
+        <v>4232.95</v>
       </c>
       <c r="I69" t="n">
         <v>4182.248927725919</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="K69" t="n">
-        <v>26.86</v>
+        <v>24.04</v>
       </c>
       <c r="L69" t="n">
         <v>3.11</v>
@@ -4374,7 +5201,7 @@
         <v>5</v>
       </c>
       <c r="N69" t="n">
-        <v>3.04</v>
+        <v>3.86</v>
       </c>
       <c r="O69" t="n">
         <v>-4.11</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>5</v>
+      </c>
+      <c r="U69" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="70">
@@ -4410,22 +5249,22 @@
         <v>8.44</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45701</v>
+        <v>45702</v>
       </c>
       <c r="H70" t="n">
-        <v>3956.55</v>
+        <v>3862.4</v>
       </c>
       <c r="I70" t="n">
         <v>3923.657466019024</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K70" t="n">
-        <v>-6.53</v>
+        <v>-8.75</v>
       </c>
       <c r="L70" t="n">
-        <v>6.8</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="M70" t="n">
         <v>0.27</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>10.72</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45758</v>
+        <v>45762</v>
       </c>
       <c r="H71" t="n">
-        <v>3666</v>
+        <v>3803.9</v>
       </c>
       <c r="I71" t="n">
         <v>3799.587642986286</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="K71" t="n">
-        <v>5.08</v>
+        <v>1.51</v>
       </c>
       <c r="L71" t="n">
         <v>3.07</v>
       </c>
       <c r="M71" t="n">
-        <v>2.07</v>
+        <v>2.26</v>
       </c>
       <c r="N71" t="n">
-        <v>3.46</v>
+        <v>3.76</v>
       </c>
       <c r="O71" t="n">
         <v>-2.38</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>10.9</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="H72" t="n">
-        <v>5539</v>
+        <v>5309</v>
       </c>
       <c r="I72" t="n">
         <v>5351.871285048627</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="K72" t="n">
-        <v>45.61</v>
+        <v>39.57</v>
       </c>
       <c r="L72" t="n">
         <v>3.67</v>
@@ -4545,7 +5408,7 @@
         <v>2.22</v>
       </c>
       <c r="N72" t="n">
-        <v>3.33</v>
+        <v>4.15</v>
       </c>
       <c r="O72" t="n">
         <v>3.76</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>139</v>
+        <v>140</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>8</v>
+      </c>
+      <c r="U72" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>8.109999999999999</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="H73" t="n">
-        <v>5538.5</v>
+        <v>5798.5</v>
       </c>
       <c r="I73" t="n">
         <v>5643.810976348906</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K73" t="n">
-        <v>-4.32</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>6.04</v>
+        <v>9.44</v>
       </c>
       <c r="M73" t="n">
-        <v>0.82</v>
+        <v>0.91</v>
       </c>
       <c r="N73" t="n">
-        <v>2.15</v>
+        <v>4.69</v>
       </c>
       <c r="O73" t="n">
         <v>-4.15</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S73" t="b">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
+        <v>1</v>
+      </c>
+      <c r="U73" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>8.949999999999999</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="H74" t="n">
-        <v>6001</v>
+        <v>5945.5</v>
       </c>
       <c r="I74" t="n">
         <v>5995.184354680262</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K74" t="n">
-        <v>3.49</v>
+        <v>2.54</v>
       </c>
       <c r="L74" t="n">
         <v>3.92</v>
@@ -4668,7 +5555,19 @@
         <v>1</v>
       </c>
       <c r="Q74" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S74" t="b">
+        <v>1</v>
+      </c>
+      <c r="T74" t="n">
+        <v>2</v>
+      </c>
+      <c r="U74" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>7.3</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="H75" t="n">
-        <v>5933</v>
+        <v>5985.5</v>
       </c>
       <c r="I75" t="n">
         <v>5949.236974646342</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="K75" t="n">
-        <v>0.21</v>
+        <v>-0.67</v>
       </c>
       <c r="L75" t="n">
         <v>1.67</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="76">
@@ -4752,28 +5663,28 @@
         <v>6.36</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46041</v>
+        <v>46042</v>
       </c>
       <c r="H76" t="n">
-        <v>5762.5</v>
+        <v>5580.5</v>
       </c>
       <c r="I76" t="n">
         <v>5636.421932386276</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K76" t="n">
-        <v>-3.73</v>
+        <v>-6.77</v>
       </c>
       <c r="L76" t="n">
-        <v>6.61</v>
+        <v>7.19</v>
       </c>
       <c r="M76" t="n">
         <v>0.96</v>
       </c>
       <c r="N76" t="n">
-        <v>2.19</v>
+        <v>3.16</v>
       </c>
       <c r="O76" t="n">
         <v>0.88</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>10</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="H77" t="n">
-        <v>5763</v>
+        <v>5851.5</v>
       </c>
       <c r="I77" t="n">
         <v>5807.988856279503</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K77" t="n">
-        <v>-3.27</v>
+        <v>-4.86</v>
       </c>
       <c r="L77" t="n">
-        <v>4.74</v>
+        <v>5.33</v>
       </c>
       <c r="M77" t="n">
         <v>1.97</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>9.57</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="H78" t="n">
-        <v>5394.5</v>
+        <v>5206</v>
       </c>
       <c r="I78" t="n">
         <v>5318.752341656271</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K78" t="n">
-        <v>-7.81</v>
+        <v>-11.03</v>
       </c>
       <c r="L78" t="n">
-        <v>8.779999999999999</v>
+        <v>11.68</v>
       </c>
       <c r="M78" t="n">
         <v>2.54</v>
       </c>
       <c r="N78" t="n">
-        <v>3.24</v>
+        <v>3.49</v>
       </c>
       <c r="O78" t="n">
         <v>1.54</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>2</v>
+      </c>
+      <c r="U78" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>11.61</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="H79" t="n">
-        <v>4987.1</v>
+        <v>5173.8</v>
       </c>
       <c r="I79" t="n">
         <v>5102.9284204731</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K79" t="n">
-        <v>4.2</v>
+        <v>0.62</v>
       </c>
       <c r="L79" t="n">
         <v>5.42</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>5</v>
+      </c>
+      <c r="U79" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="80">
@@ -4980,19 +5939,19 @@
         <v>7.94</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="H80" t="n">
-        <v>5600</v>
+        <v>5450</v>
       </c>
       <c r="I80" t="n">
         <v>5454.660159177382</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="K80" t="n">
-        <v>8.24</v>
+        <v>5.34</v>
       </c>
       <c r="L80" t="n">
         <v>3.74</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S80" t="b">
+        <v>1</v>
+      </c>
+      <c r="T80" t="n">
+        <v>3</v>
+      </c>
+      <c r="U80" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="81">
@@ -5037,19 +6008,19 @@
         <v>7.96</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46322</v>
+        <v>46323</v>
       </c>
       <c r="H81" t="n">
-        <v>5218.5</v>
+        <v>5348.5</v>
       </c>
       <c r="I81" t="n">
         <v>5287.32522141458</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K81" t="n">
-        <v>4.25</v>
+        <v>1.86</v>
       </c>
       <c r="L81" t="n">
         <v>3.83</v>
@@ -5067,7 +6038,19 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R81" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="n">
+        <v>3</v>
+      </c>
+      <c r="U81" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="82">
@@ -5118,6 +6101,12 @@
       <c r="Q82" t="n">
         <v>1</v>
       </c>
+      <c r="R82" s="3" t="n">
+        <v>46350</v>
+      </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10076,7 +11065,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>52.1</v>
+        <v>53.8</v>
       </c>
     </row>
     <row r="6">
@@ -10086,7 +11075,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7">
@@ -10096,7 +11085,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>239</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
@@ -10106,7 +11095,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -10116,7 +11105,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72.5</v>
+        <v>73.8</v>
       </c>
     </row>
     <row r="10">
@@ -10126,7 +11115,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98.3</v>
+        <v>101.1</v>
       </c>
     </row>
     <row r="11">
@@ -10136,7 +11125,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="12">
@@ -10146,7 +11135,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -10156,7 +11145,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>38.8</v>
+        <v>36.2</v>
       </c>
     </row>
     <row r="14">
@@ -10166,7 +11155,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.93</v>
+        <v>0.14</v>
       </c>
     </row>
     <row r="15">
@@ -10176,7 +11165,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.95</v>
+        <v>1.44</v>
       </c>
     </row>
     <row r="16">
@@ -10186,7 +11175,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.92</v>
+        <v>-1.17</v>
       </c>
     </row>
     <row r="17">
@@ -10196,7 +11185,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>49.14</v>
+        <v>46.95</v>
       </c>
     </row>
     <row r="18">
@@ -10206,7 +11195,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>48.8</v>
+        <v>38.8</v>
       </c>
     </row>
     <row r="19">
@@ -10216,7 +11205,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.05</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="20">
@@ -10226,7 +11215,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.65</v>
+        <v>5.42</v>
       </c>
     </row>
     <row r="21">
@@ -10236,7 +11225,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.25</v>
+        <v>19.91</v>
       </c>
     </row>
     <row r="22">
@@ -10246,7 +11235,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23">
@@ -10256,7 +11245,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -10266,7 +11255,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="25">
@@ -10286,7 +11275,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.35</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="27">
@@ -10296,7 +11285,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>12.63</v>
+        <v>13.59</v>
       </c>
     </row>
     <row r="28">
@@ -10306,7 +11295,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
     </row>
     <row r="29">
